--- a/FP326_result.xlsx
+++ b/FP326_result.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put CD on the chair and Open the Book</t>
+          <t>Put pen and creditcard in the drawer and put the pen on the desk</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -507,14 +507,14 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>86.11</v>
       </c>
       <c r="F2" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>FAILED (Execution Errors)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -539,10 +539,10 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>100</v>
+        <v>86.11</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
     </row>
   </sheetData>
